--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -2229,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BZ160"/>
+  <dimension ref="A1:BZ169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28.625" style="59" customWidth="1"/>
@@ -14083,9 +14083,9 @@
         <v>206</v>
       </c>
       <c r="C61" s="4"/>
-      <c r="D61" s="6" t="s">
-        <v>207</v>
-      </c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D61" s="6" t="str">
+        <x:v>使用凝胶装瓶器装瓶的盐水，瓶子是用水凝胶做的。无论多口渴都不建议直接饮用，高浓度盐水会导致严重的脱水。可拖入燃料蒸馏器蒸馏为淡水。也可在点燃的野炊营火中加热15分钟，1盐水得到1盐。</x:v>
+      </x:c>
       <c r="E61" s="4"/>
       <c r="F61" s="12">
         <v>1</v>
@@ -14198,15 +14198,15 @@
       <c r="AT61" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AU61" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AV61" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW61" s="4" t="s">
-        <v>64</v>
-      </c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU61" s="4" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV61" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW61" s="4" t="str">
+        <x:v>盐</x:v>
+      </x:c>
       <c r="AX61" s="21" t="s">
         <v>62</v>
       </c>
@@ -14825,9 +14825,9 @@
       <c r="BG64" s="4">
         <v>0.5</v>
       </c>
-      <c r="BH64" s="4" t="s">
-        <v>217</v>
-      </c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH64" s="4" t="str">
+        <x:v>12_26_5_32_-5_40</x:v>
+      </x:c>
       <c r="BI64" s="4" t="s">
         <v>218</v>
       </c>
@@ -16005,9 +16005,9 @@
       <c r="BG70" s="4">
         <v>0.7</v>
       </c>
-      <c r="BH70" s="4" t="s">
-        <v>235</v>
-      </c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH70" s="4" t="str">
+        <x:v>4_16_-2_24_-10_32</x:v>
+      </x:c>
       <c r="BI70" s="4" t="s">
         <v>177</v>
       </c>
@@ -26988,10 +26988,12 @@
       <c r="BJ126" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BK126" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL126" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK126" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL126" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <c r="BM126" s="4" t="s">
         <v>62</v>
       </c>
@@ -29370,10 +29372,12 @@
       <c r="BJ139" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BK139" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL139" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK139" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL139" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <c r="BM139" s="4" t="s">
         <v>62</v>
       </c>
@@ -29982,10 +29986,12 @@
       <c r="BJ143" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BK143" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL143" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK143" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL143" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <c r="BM143" s="4" t="s">
         <v>62</v>
       </c>
@@ -30706,10 +30712,12 @@
       <c r="BJ147" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BK147" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL147" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK147" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL147" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <c r="BM147" s="4" t="s">
         <v>62</v>
       </c>
@@ -32692,10 +32700,12 @@
       <c r="BJ157" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BK157" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL157" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK157" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL157" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <c r="BM157" s="4" t="s">
         <v>62</v>
       </c>
@@ -32989,16 +32999,1664 @@
       <c r="BX160" s="68"/>
       <c r="BY160" s="68"/>
     </row>
+    <row r="161" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A161" t="str" s="9">
+        <x:v>融冰浮标</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B161" t="str" s="9">
+        <x:v>融冰浮标</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C161" t="str" s="9">
+        <x:v>未布置</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D161" t="str" s="6">
+        <x:v>放入水域通道的改装槽。每回合消耗0.2耐久；融冰时额外消耗0.8耐久并降低15冰封值。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E161" t="str" s="4">
+        <x:v>未布置</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F161" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G161" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H161" t="str" s="52">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I161" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J161" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K161" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L161" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M161" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N161" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P161" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q161" t="n" s="4">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R161" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T161" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V161" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W161" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y161" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD161" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE161" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX161" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ161" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK161" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM161" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ161" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS161" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT161" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV161" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW161" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY161" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ161" s="4"/>
+    </row>
+    <row r="162" spans="1:78" ht="42.75" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A162" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B162" t="str" s="9">
+        <x:v>融冰浮标</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C162" t="str" s="9">
+        <x:v>已布置</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D162" s="6"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E162" t="str" s="4">
+        <x:v>已布置</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F162" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G162" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H162" s="52"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J162" s="10"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N162" s="10"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P162" s="10"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R162" s="10"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T162" s="10"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V162" s="10"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX162" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS162" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV162" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW162" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY162" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ162" s="4"/>
+    </row>
+    <row r="163" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A163" t="str" s="9">
+        <x:v>牵引绳</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B163" t="str" s="9">
+        <x:v>牵引绳</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C163" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D163" s="6" t="str">
+        <x:v>用于水域地点改装。地点内移动速度增加50%，每5分钟原始移动时间消耗1耐久。不支持盐填充。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F163" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G163" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H163" t="str" s="52">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I163" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J163" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K163" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L163" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M163" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N163" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P163" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q163" t="n" s="4">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R163" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T163" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V163" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W163" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y163" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD163" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE163" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX163" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ163" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK163" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM163" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ163" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS163" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT163" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV163" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW163" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY163" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ163" s="4"/>
+    </row>
+    <row r="164" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A164" t="str" s="9">
+        <x:v>防水电缆</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B164" t="str" s="9">
+        <x:v>防水电缆</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C164" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D164" t="str" s="6">
+        <x:v>用于地点供电改装。每回合有50%概率消耗1耐久，损坏后设备断电。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F164" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G164" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H164" t="str" s="52">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I164" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J164" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K164" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L164" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M164" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N164" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P164" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q164" t="n" s="4">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R164" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T164" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V164" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W164" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y164" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD164" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE164" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX164" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ164" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK164" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM164" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ164" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS164" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT164" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV164" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW164" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY164" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ164" s="4"/>
+    </row>
+    <row r="165" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A165" t="str" s="9">
+        <x:v>隔热棉</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B165" t="str" s="9">
+        <x:v>隔热棉</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C165" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D165" t="str" s="6">
+        <x:v>用于室内地点改装，隔热等级增加1。不能重复铺设，可花15分钟拆除回收。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F165" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G165" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H165" t="str" s="52">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I165" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J165" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K165" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L165" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M165" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N165" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P165" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R165" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T165" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V165" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W165" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y165" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD165" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE165" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX165" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ165" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK165" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM165" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ165" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS165" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT165" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV165" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW165" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY165" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ165" s="4"/>
+    </row>
+    <row r="166" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A166" t="str" s="9">
+        <x:v>保温服</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B166" t="str" s="9">
+        <x:v>保温服</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C166" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D166" t="str" s="6">
+        <x:v>装备后承受15%的体温下降，其余85%每抵消1℃消耗10耐久。可用纤维或暖绒修补。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F166" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G166" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H166" t="str" s="52">
+        <x:v>Equipment</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I166" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J166" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K166" t="n" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L166" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M166" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N166" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P166" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q166" t="n" s="4">
+        <x:v>1440</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R166" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T166" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V166" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W166" t="str" s="11">
+        <x:v>Body</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y166" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD166" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE166" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX166" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ166" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK166" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM166" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ166" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS166" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT166" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV166" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW166" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY166" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ166" s="4"/>
+    </row>
+    <row r="167" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A167" t="str" s="9">
+        <x:v>暖暖贴</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B167" t="str" s="9">
+        <x:v>暖暖贴</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C167" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D167" t="str" s="6">
+        <x:v>贴在身上消耗3分钟，体温增加0.7℃，最多恢复至37.5℃。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F167" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G167" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H167" t="str" s="52">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I167" t="n" s="4">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J167" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K167" t="n" s="4">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L167" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M167" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N167" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P167" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R167" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T167" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V167" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W167" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y167" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD167" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE167" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX167" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ167" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK167" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM167" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ167" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS167" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT167" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV167" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW167" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY167" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ167" s="4"/>
+    </row>
+    <row r="168" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A168" t="str" s="9">
+        <x:v>盐</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B168" t="str" s="9">
+        <x:v>盐</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C168" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D168" s="6" t="str">
+        <x:v>盐水在野炊营火中加热15分钟得到的材料，可用于填充融冰浮标和制作物资，不能补充牵引绳耐久。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F168" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G168" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H168" t="str" s="52">
+        <x:v>Resource</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I168" t="n" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J168" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K168" t="n" s="4">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L168" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M168" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N168" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P168" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R168" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T168" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V168" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W168" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y168" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD168" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE168" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU168" s="11" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV168" s="4" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW168" s="4" t="str">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX168" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ168" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK168" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM168" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ168" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS168" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT168" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV168" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW168" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY168" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ168" s="4"/>
+    </row>
+    <row r="169" spans="1:78" ht="72" customHeight="1">
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="A169" t="str" s="9">
+        <x:v>暖绒</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="B169" t="str" s="9">
+        <x:v>暖绒</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="C169" s="9"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="D169" t="str" s="6">
+        <x:v>蓬松的保温材料，可用于制作隔热棉、保温服和补充融冰浮标。</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="E169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="F169" t="str" s="37">
+        <x:v>Resource/1</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="G169" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="H169" t="str" s="52">
+        <x:v>Resource</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="I169" t="n" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="J169" t="str" s="10">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="K169" t="n" s="4">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="L169" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="M169" t="str" s="4">
+        <x:v>默认质感</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="N169" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="O169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="P169" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Q169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="R169" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="S169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="T169" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="U169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="V169" t="str" s="10">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="W169" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="X169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Y169" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="Z169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AA169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AB169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AC169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AD169" t="n" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AE169" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AF169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AG169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AH169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AI169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AJ169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AK169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AL169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AM169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AN169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AO169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AP169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AQ169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AR169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AS169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AT169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AU169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AV169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AW169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AX169" t="str" s="21">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AY169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="AZ169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BA169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BB169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BC169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BD169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BE169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BF169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BG169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BH169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BI169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BJ169" t="str" s="4">
+        <x:v>/</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BK169" t="str" s="11">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BL169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BM169" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BN169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BO169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BP169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BQ169" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BR169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BS169" s="5"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BT169" t="str" s="4">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BU169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BV169" s="11"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BW169" s="21"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BX169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BY169" s="4"/>
+      <x:c xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="BZ169" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ2:BQ1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Single,AOE,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576 BT2:BT158 AE2:AE158 AC2:AC160 AB2:AB1048576 BM2:BM1048576 Z2:Z1048576 BK2:BK1048576 G2:G1048576 AG2:AG1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576 BT2:BT169 AE2:AE169 AC2:AC169 AB2:AB1048576 BM2:BM1048576 Z2:Z1048576 BK2:BK1048576 G2:G1048576 AG2:AG1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"true,false,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576 BC121:BC148 AX2:AX158 AQ2:AQ1048576 V2:V1048576 T2:T1048576 R2:R1048576 X2:X1048576 N2:N1048576 J2:J1048576 AU2:AU1048576 P2:P1048576 AY2:BB1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576 BC121:BC148 AX2:AX169 AQ2:AQ1048576 V2:V1048576 T2:T1048576 R2:R1048576 X2:X1048576 N2:N1048576 J2:J1048576 AU2:AU1048576 P2:P1048576 AY2:BB1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"false,true,"</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR2:BR1048576" xr:uid="{00000000-0002-0000-0000-000007000000}"/>
